--- a/reports/pdf_rolling5_20260714.xlsx
+++ b/reports/pdf_rolling5_20260714.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-07 ~ 2026-07-14  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-07 ~ 2026-07-14  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1620000000</v>
+        <v>1597500000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>3.67%→3.84%</t>
+          <t>2.61%→2.93%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
@@ -1351,23 +1351,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1597500000</v>
+        <v>416500000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.93%</t>
+          <t>2.75%→2.96%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
@@ -1379,23 +1379,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>416500000</v>
+        <v>1620000000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2.75%→2.96%</t>
+          <t>3.67%→3.84%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G23" s="17" t="n"/>
@@ -1429,737 +1429,1023 @@
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="20" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="20" t="n"/>
-    </row>
-    <row r="30" ht="19" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="20" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억   ·   현금 52억(1.9%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 4종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="8" t="n"/>
+      <c r="J29" s="8" t="n"/>
+      <c r="K29" s="8" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>201</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>5977358100</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>6.49%→8.34%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>549→750</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>-86</v>
+      </c>
+      <c r="I31" s="15" t="n">
+        <v>-7362700800</v>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>4.76%→2.24%</t>
+        </is>
+      </c>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>156→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>엘앤씨바이오  (신규)</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>6627103000</v>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.48%</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>0→139</t>
+        </is>
+      </c>
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <v>-4295251800</v>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>3.28%→1.37%</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>150→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치  (신규)</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>7935305000</v>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.97%</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>0→35</t>
+        </is>
+      </c>
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>-66</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <v>-8439446400</v>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>9.28%→8.13%</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>236→170</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>1321304600</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>1.32%→1.71%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>42→59</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-58</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-1519901600</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>2.38%→1.87%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>249→191</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <v>-4445280000</v>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>3.71%→2.49%</t>
+        </is>
+      </c>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>100→60</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억   ·   현금 52억(2.1%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="19" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억   ·   현금 5억(100.0%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 10종목  /  매도 14종목</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="8" t="n"/>
+      <c r="J41" s="8" t="n"/>
+      <c r="K41" s="8" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D34" s="9" t="inlineStr">
+      <c r="D42" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E34" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G42" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J34" s="9" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>209</v>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>158641450</v>
-      </c>
-      <c r="D35" s="12" t="inlineStr">
-        <is>
-          <t>6.37%→6.79%</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>3,020→3,229</t>
-        </is>
-      </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>-318</v>
-      </c>
-      <c r="I35" s="15" t="n">
-        <v>-107444250</v>
-      </c>
-      <c r="J35" s="16" t="inlineStr">
-        <is>
-          <t>2.87%→2.56%</t>
-        </is>
-      </c>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>3,054→2,736</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n">
-        <v>85</v>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>342103750</v>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>7.03%→7.96%</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>629→714</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>서부T&amp;D</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>-33017400</v>
-      </c>
-      <c r="J36" s="16" t="inlineStr">
-        <is>
-          <t>0.19%→0.09%</t>
-        </is>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>73→37</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>168300000</v>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>2.08%→2.54%</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>196→240</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>-110160000</v>
-      </c>
-      <c r="J37" s="16" t="inlineStr">
-        <is>
-          <t>6.23%→5.91%</t>
-        </is>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>733→697</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>92004000</v>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>2.62%→2.87%</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>451→495</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>채비  (편출)</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>-17051000</v>
-      </c>
-      <c r="J38" s="16" t="inlineStr">
-        <is>
-          <t>0.05%→0.00%</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>34→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>네패스아크</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>54060000</v>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>0.20%→0.35%</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>21→37</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>더핑크퐁컴퍼니</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-30951900</v>
-      </c>
-      <c r="J39" s="16" t="inlineStr">
-        <is>
-          <t>0.21%→0.12%</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>82→48</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t>알멕</t>
-        </is>
-      </c>
-      <c r="B40" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>39716250</v>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>0.61%→0.72%</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>83→98</t>
-        </is>
-      </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>삼현  (편출)</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I40" s="15" t="n">
-        <v>-78259500</v>
-      </c>
-      <c r="J40" s="16" t="inlineStr">
-        <is>
-          <t>0.22%→0.00%</t>
-        </is>
-      </c>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>27→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="B41" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>37740000</v>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>1.20%→1.30%</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>114→124</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I41" s="15" t="n">
-        <v>-70762500</v>
-      </c>
-      <c r="J41" s="16" t="inlineStr">
-        <is>
-          <t>0.75%→0.55%</t>
-        </is>
-      </c>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>95→70</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="10" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C42" s="11" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>2.51%→2.74%</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>85→93</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>오로스테크놀로지</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I42" s="15" t="n">
-        <v>-35249500</v>
-      </c>
-      <c r="J42" s="16" t="inlineStr">
-        <is>
-          <t>0.38%→0.28%</t>
-        </is>
-      </c>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>85→63</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>39168000</v>
+        <v>158641450</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.89%→0.99%</t>
+          <t>6.37%→6.79%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>49→55</t>
+          <t>3,020→3,229</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-14</v>
+        <v>-318</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-37663500</v>
+        <v>-107444250</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>2.87%→2.56%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>3,054→2,736</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>342103750</v>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>7.03%→7.96%</t>
+        </is>
+      </c>
+      <c r="E44" s="13" t="inlineStr">
+        <is>
+          <t>629→714</t>
+        </is>
+      </c>
+      <c r="G44" s="14" t="inlineStr">
+        <is>
+          <t>서부T&amp;D</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I44" s="15" t="n">
+        <v>-33017400</v>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>0.19%→0.09%</t>
+        </is>
+      </c>
+      <c r="K44" s="13" t="inlineStr">
+        <is>
+          <t>73→37</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>168300000</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>2.08%→2.54%</t>
+        </is>
+      </c>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>196→240</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H45" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I45" s="15" t="n">
+        <v>-110160000</v>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>6.23%→5.91%</t>
+        </is>
+      </c>
+      <c r="K45" s="13" t="inlineStr">
+        <is>
+          <t>733→697</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>92004000</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>2.62%→2.87%</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>451→495</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>채비  (편출)</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I46" s="15" t="n">
+        <v>-17051000</v>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>0.05%→0.00%</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>34→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>네패스아크</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>54060000</v>
+      </c>
+      <c r="D47" s="12" t="inlineStr">
+        <is>
+          <t>0.20%→0.35%</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>21→37</t>
+        </is>
+      </c>
+      <c r="G47" s="14" t="inlineStr">
+        <is>
+          <t>더핑크퐁컴퍼니</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I47" s="15" t="n">
+        <v>-30951900</v>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>0.21%→0.12%</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>82→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>39716250</v>
+      </c>
+      <c r="D48" s="12" t="inlineStr">
+        <is>
+          <t>0.61%→0.72%</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>83→98</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>삼현  (편출)</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-78259500</v>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>0.22%→0.00%</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>37740000</v>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>1.20%→1.30%</t>
+        </is>
+      </c>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>114→124</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-70762500</v>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>0.75%→0.55%</t>
+        </is>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>95→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="D50" s="12" t="inlineStr">
+        <is>
+          <t>2.51%→2.74%</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>85→93</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-35249500</v>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>0.38%→0.28%</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>85→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>39168000</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>0.89%→0.99%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>49→55</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>하이록코리아</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-37663500</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.10%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>27→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
           <t>코스메카코리아  (신규)</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n">
+      <c r="B52" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C52" s="11" t="n">
         <v>35275000</v>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>0.00%→0.10%</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>0→5</t>
         </is>
       </c>
-      <c r="G44" s="14" t="inlineStr">
+      <c r="G52" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H44" s="15" t="n">
+      <c r="H52" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I44" s="15" t="n">
+      <c r="I52" s="15" t="n">
         <v>-150501000</v>
       </c>
-      <c r="J44" s="16" t="inlineStr">
+      <c r="J52" s="16" t="inlineStr">
         <is>
           <t>3.44%→3.02%</t>
         </is>
       </c>
-      <c r="K44" s="13" t="inlineStr">
+      <c r="K52" s="13" t="inlineStr">
         <is>
           <t>107→94</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="17" t="n"/>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="17" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
-      <c r="G45" s="14" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="17" t="n"/>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="G53" s="14" t="inlineStr">
         <is>
           <t>디앤디파마텍</t>
         </is>
       </c>
-      <c r="H45" s="15" t="n">
+      <c r="H53" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I45" s="15" t="n">
+      <c r="I53" s="15" t="n">
         <v>-71655000</v>
       </c>
-      <c r="J45" s="16" t="inlineStr">
+      <c r="J53" s="16" t="inlineStr">
         <is>
           <t>0.96%→0.75%</t>
         </is>
       </c>
-      <c r="K45" s="13" t="inlineStr">
+      <c r="K53" s="13" t="inlineStr">
         <is>
           <t>48→38</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="17" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="G46" s="14" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="17" t="n"/>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="G54" s="14" t="inlineStr">
         <is>
           <t>ISC</t>
         </is>
       </c>
-      <c r="H46" s="15" t="n">
+      <c r="H54" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I46" s="15" t="n">
+      <c r="I54" s="15" t="n">
         <v>-89964000</v>
       </c>
-      <c r="J46" s="16" t="inlineStr">
+      <c r="J54" s="16" t="inlineStr">
         <is>
           <t>1.71%→1.46%</t>
         </is>
       </c>
-      <c r="K46" s="13" t="inlineStr">
+      <c r="K54" s="13" t="inlineStr">
         <is>
           <t>48→41</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="G47" s="14" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="17" t="n"/>
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="G55" s="14" t="inlineStr">
         <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="H47" s="15" t="n">
+      <c r="H55" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I47" s="15" t="n">
+      <c r="I55" s="15" t="n">
         <v>-19176000</v>
       </c>
-      <c r="J47" s="16" t="inlineStr">
+      <c r="J55" s="16" t="inlineStr">
         <is>
           <t>0.75%→0.70%</t>
         </is>
       </c>
-      <c r="K47" s="13" t="inlineStr">
+      <c r="K55" s="13" t="inlineStr">
         <is>
           <t>85→79</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="n"/>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="G48" s="14" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="G56" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H48" s="15" t="n">
+      <c r="H56" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I48" s="15" t="n">
+      <c r="I56" s="15" t="n">
         <v>-59160000</v>
       </c>
-      <c r="J48" s="16" t="inlineStr">
+      <c r="J56" s="16" t="inlineStr">
         <is>
           <t>2.57%→2.40%</t>
         </is>
       </c>
-      <c r="K48" s="13" t="inlineStr">
+      <c r="K56" s="13" t="inlineStr">
         <is>
           <t>47→44</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
+    <row r="58" ht="19" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억   ·   현금 18억(3.2%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="19" customHeight="1">
-      <c r="A53" s="19" t="inlineStr">
+    <row r="61" ht="19" customHeight="1">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B53" s="20" t="n"/>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="20" t="n"/>
-      <c r="G53" s="20" t="n"/>
-      <c r="H53" s="20" t="n"/>
-      <c r="I53" s="20" t="n"/>
-      <c r="J53" s="20" t="n"/>
-      <c r="K53" s="20" t="n"/>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="20" t="n"/>
+      <c r="G61" s="20" t="n"/>
+      <c r="H61" s="20" t="n"/>
+      <c r="I61" s="20" t="n"/>
+      <c r="J61" s="20" t="n"/>
+      <c r="K61" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A53:K53"/>
+  <mergeCells count="18">
+    <mergeCell ref="A61:K61"/>
+    <mergeCell ref="A58:K58"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="G29:K29"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A30:K30"/>
+    <mergeCell ref="A59:K59"/>
     <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G33:K33"/>
-    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="G41:K41"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A37:K37"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20260714.xlsx
+++ b/reports/pdf_rolling5_20260714.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,826억   ·   현금 120억(2.4%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 18종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,599억   ·   현금 119억(2.4%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 18종목  /  매도 15종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>164</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1564560000</v>
+        <v>1552043520</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-54</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-926100000</v>
+        <v>-918691200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>93</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1003470000</v>
+        <v>995442240</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-52</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1731600000</v>
+        <v>-1717747200</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>66</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5068800000</v>
+        <v>5028249600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-37</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1148850000</v>
+        <v>-1139659200</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>546960000</v>
+        <v>542584320</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-25</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-4442500000</v>
+        <v>-4406960000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>39</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1468350000</v>
+        <v>1456603200</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-23</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2875000000</v>
+        <v>-2852000000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>21</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1770300000</v>
+        <v>1756137600</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-20</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-947000000</v>
+        <v>-939424000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>20</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1144000000</v>
+        <v>1134848000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-19</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1377500000</v>
+        <v>-1366480000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>19</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1428800000</v>
+        <v>1417369600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -992,23 +992,23 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-885700000</v>
+        <v>-525313600</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.93%→0.63%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>75→58</t>
+          <t>32→15</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
         <v>16</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1425600000</v>
+        <v>1414195200</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1036,23 +1036,23 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-17</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-529550000</v>
+        <v>-878614400</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.93%→0.63%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>32→15</t>
+          <t>75→58</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>479400000</v>
+        <v>475564800</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>-16</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-3030400000</v>
+        <v>-3006156800</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>463650000</v>
+        <v>459940800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>-12</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-477000000</v>
+        <v>-473184000</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>422000000</v>
+        <v>467728000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.25%→0.32%</t>
+          <t>1.86%→1.84%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1175,7 +1175,7 @@
         <v>-11</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-897600000</v>
+        <v>-890419200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>471500000</v>
+        <v>418624000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.86%→1.84%</t>
+          <t>0.25%→0.32%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1219,7 +1219,7 @@
         <v>-10</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-503000000</v>
+        <v>-498976000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>981600000</v>
+        <v>973747200</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-987000000</v>
+        <v>-979104000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>953400000</v>
+        <v>945772800</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>-4</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-481200000</v>
+        <v>-477350400</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1597500000</v>
+        <v>1607040000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.93%</t>
+          <t>3.67%→3.84%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
@@ -1358,7 +1358,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>416500000</v>
+        <v>413168000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1379,23 +1379,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1620000000</v>
+        <v>1584720000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>3.67%→3.84%</t>
+          <t>2.61%→2.93%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G23" s="17" t="n"/>
@@ -1407,7 +1407,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,371억   ·   현금 38억(0.9%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,227억   ·   현금 38억(0.9%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1431,7 +1431,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,815억   ·   현금 52억(1.9%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 52억(1.9%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1527,7 +1527,7 @@
         <v>201</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>5977358100</v>
+        <v>5968644750</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>-86</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-7362700800</v>
+        <v>-7351968000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>139</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>6627103000</v>
+        <v>6617442500</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
         <v>-81</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-4295251800</v>
+        <v>-4288990500</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         <v>35</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>7935305000</v>
+        <v>7923737500</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>-66</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-8439446400</v>
+        <v>-8427144000</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>17</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>1321304600</v>
+        <v>1319378500</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>-58</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-1519901600</v>
+        <v>-1517686000</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>-40</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-4445280000</v>
+        <v>-4438800000</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
     <row r="37" ht="19" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,598억   ·   현금 52억(2.1%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 53억(2.1%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -1748,7 +1748,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 363억   ·   현금 5억(100.0%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 10종목  /  매도 14종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 344억   ·   현금 5억(100.0%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 10종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1844,11 +1844,11 @@
         <v>209</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>158641450</v>
+        <v>151713100</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>6.37%→6.79%</t>
+          <t>6.42%→6.86%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1865,11 +1865,11 @@
         <v>-318</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-107444250</v>
+        <v>-105146700</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>2.87%→2.56%</t>
+          <t>2.96%→2.65%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1888,11 +1888,11 @@
         <v>85</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>342103750</v>
+        <v>283581250</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>7.03%→7.96%</t>
+          <t>6.15%→6.97%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1902,111 +1902,111 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-33017400</v>
+        <v>-100827000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.19%→0.09%</t>
+          <t>6.01%→5.71%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>168300000</v>
+        <v>77792000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.08%→2.54%</t>
+          <t>2.34%→2.56%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>196→240</t>
+          <t>451→495</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-110160000</v>
+        <v>-33323400</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>6.23%→5.91%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>44</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>92004000</v>
+        <v>162129000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.62%→2.87%</t>
+          <t>2.12%→2.59%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>451→495</t>
+          <t>196→240</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-17051000</v>
+        <v>-29189000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.21%→0.12%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
         <v>16</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>54060000</v>
+        <v>52360000</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2034,23 +2034,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-30951900</v>
+        <v>-15432600</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.12%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
@@ -2064,11 +2064,11 @@
         <v>15</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>39716250</v>
+        <v>35572500</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>0.61%→0.72%</t>
+          <t>0.58%→0.68%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -2085,11 +2085,11 @@
         <v>-27</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-78259500</v>
+        <v>-71833500</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.22%→0.00%</t>
+          <t>0.21%→0.00%</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
@@ -2108,11 +2108,11 @@
         <v>10</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>37740000</v>
+        <v>35615000</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>1.20%→1.30%</t>
+          <t>1.19%→1.29%</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -2129,11 +2129,11 @@
         <v>-25</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-70762500</v>
+        <v>-59818750</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.55%</t>
+          <t>0.67%→0.49%</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
@@ -2152,11 +2152,11 @@
         <v>8</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>85000000</v>
+        <v>84864000</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>2.51%→2.74%</t>
+          <t>2.64%→2.89%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -2173,11 +2173,11 @@
         <v>-22</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-35249500</v>
+        <v>-34782000</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.38%→0.28%</t>
+          <t>0.39%→0.29%</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
@@ -2196,11 +2196,11 @@
         <v>6</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>39168000</v>
+        <v>36006000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.89%→0.99%</t>
+          <t>0.86%→0.97%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -2217,11 +2217,11 @@
         <v>-14</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-37663500</v>
+        <v>-36592500</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>0.21%→0.10%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
@@ -2240,11 +2240,11 @@
         <v>5</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>35275000</v>
+        <v>37697500</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.10%</t>
+          <t>0.00%→0.11%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -2261,11 +2261,11 @@
         <v>-13</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-150501000</v>
+        <v>-154810500</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>3.44%→3.02%</t>
+          <t>3.73%→3.28%</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
@@ -2289,11 +2289,11 @@
         <v>-10</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-71655000</v>
+        <v>-65450000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.96%→0.75%</t>
+          <t>0.92%→0.73%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2317,11 +2317,11 @@
         <v>-7</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-89964000</v>
+        <v>-91332500</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>1.71%→1.46%</t>
+          <t>1.83%→1.57%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2345,11 +2345,11 @@
         <v>-6</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-19176000</v>
+        <v>-19558500</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.75%→0.70%</t>
+          <t>0.81%→0.75%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2373,11 +2373,11 @@
         <v>-3</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-59160000</v>
+        <v>-58522500</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.57%→2.40%</t>
+          <t>2.69%→2.51%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2389,7 +2389,7 @@
     <row r="58" ht="19" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 579억   ·   현금 18억(3.2%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 18억(3.2%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260714.xlsx
+++ b/reports/pdf_rolling5_20260714.xlsx
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>467728000</v>
+        <v>418624000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.86%→1.84%</t>
+          <t>0.25%→0.32%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>418624000</v>
+        <v>467728000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.25%→0.32%</t>
+          <t>1.86%→1.84%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1607040000</v>
+        <v>1584720000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>3.67%→3.84%</t>
+          <t>2.61%→2.93%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G21" s="17" t="n"/>
@@ -1379,23 +1379,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1584720000</v>
+        <v>1607040000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.93%</t>
+          <t>3.67%→3.84%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G23" s="17" t="n"/>
@@ -1902,111 +1902,111 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>씨어스</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-100827000</v>
+        <v>-33323400</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>6.01%→5.71%</t>
+          <t>0.20%→0.10%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>733→697</t>
+          <t>73→37</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>77792000</v>
+        <v>162129000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.34%→2.56%</t>
+          <t>2.12%→2.59%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>451→495</t>
+          <t>196→240</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-36</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-33323400</v>
+        <v>-100827000</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>6.01%→5.71%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>73→37</t>
+          <t>733→697</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>44</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>162129000</v>
+        <v>77792000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.12%→2.59%</t>
+          <t>2.34%→2.56%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>196→240</t>
+          <t>451→495</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-29189000</v>
+        <v>-15432600</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.12%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
@@ -2034,23 +2034,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-15432600</v>
+        <v>-29189000</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.21%→0.12%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260714.xlsx
+++ b/reports/pdf_rolling5_20260714.xlsx
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>418624000</v>
+        <v>467728000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>0.25%→0.32%</t>
+          <t>1.86%→1.84%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>467728000</v>
+        <v>418624000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.86%→1.84%</t>
+          <t>0.25%→0.32%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1925,23 +1925,23 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>에프앤가이드</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
         <v>44</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>162129000</v>
+        <v>77792000</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.12%→2.59%</t>
+          <t>2.34%→2.56%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>196→240</t>
+          <t>451→495</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -1969,44 +1969,44 @@
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>에프앤가이드</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
         <v>44</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>77792000</v>
+        <v>162129000</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>2.34%→2.56%</t>
+          <t>2.12%→2.59%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>451→495</t>
+          <t>196→240</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-15432600</v>
+        <v>-29189000</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.05%→0.00%</t>
+          <t>0.21%→0.12%</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
@@ -2034,23 +2034,23 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-29189000</v>
+        <v>-15432600</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.12%</t>
+          <t>0.05%→0.00%</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260714.xlsx
+++ b/reports/pdf_rolling5_20260714.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,599억   ·   현금 119억(2.4%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 18종목  /  매도 15종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,599억   ·   현금 123억(2.6%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 19종목  /  매도 22종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -667,612 +667,612 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>164</v>
+        <v>265</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1552043520</v>
+        <v>2368548800</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>0.67%→0.98%</t>
+          <t>0.67%→1.16%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>329→493</t>
+          <t>329→594</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-54</v>
+        <v>-66</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-918691200</v>
+        <v>-1843036800</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
-          <t>0.35%→0.19%</t>
+          <t>0.77%→0.41%</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>108→54</t>
+          <t>133→67</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>파두  (신규)</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>995442240</v>
+        <v>6793414400</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>1.27%→1.49%</t>
+          <t>0.00%→1.49%</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>572→665</t>
+          <t>0→97</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-52</v>
+        <v>-54</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-1717747200</v>
+        <v>-904227840</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>0.77%→0.56%</t>
+          <t>0.35%→0.20%</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>133→81</t>
+          <t>108→54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>파두  (신규)</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>5028249600</v>
+        <v>1004667840</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.05%</t>
+          <t>1.27%→1.57%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>0→66</t>
+          <t>572→665</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>오스코텍</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-37</v>
+        <v>-50</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1139659200</v>
+        <v>-1946800000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>1.27%→0.92%</t>
+          <t>2.19%→1.44%</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>179→142</t>
+          <t>219→169</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>저스템</t>
+          <t>샘씨엔에스  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>542584320</v>
+        <v>1022613120</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.40%→0.57%</t>
+          <t>0.00%→0.22%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>173→216</t>
+          <t>0→83</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-25</v>
+        <v>-37</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-4406960000</v>
+        <v>-1082768000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>9.44%→9.28%</t>
+          <t>1.27%→0.91%</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>276→251</t>
+          <t>179→142</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1456603200</v>
+        <v>496942400</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>0.22%→0.52%</t>
+          <t>0.40%→0.55%</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>27→66</t>
+          <t>173→216</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>노바렉스</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-23</v>
+        <v>-35</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-2852000000</v>
+        <v>-492676800</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.06%→0.44%</t>
+          <t>0.49%→0.44%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>40→17</t>
+          <t>177→142</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>디앤디파마텍</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B11" s="11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1756137600</v>
+        <v>1381161600</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>0.95%→1.40%</t>
+          <t>0.22%→0.51%</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>59→80</t>
+          <t>27→66</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-939424000</v>
+        <v>-912144000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>2.19%→1.96%</t>
+          <t>1.43%→1.15%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>219→199</t>
+          <t>202→172</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>가온칩스</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1134848000</v>
+        <v>2284873600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>1.21%→1.87%</t>
+          <t>2.72%→3.41%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>137→157</t>
+          <t>180→211</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-19</v>
+        <v>-25</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1366480000</v>
+        <v>-4622720000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.18%</t>
+          <t>9.44%→10.17%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>31→12</t>
+          <t>276→251</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>티에프이</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1417369600</v>
+        <v>904704000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>2.72%→3.11%</t>
+          <t>0.46%→0.68%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>180→199</t>
+          <t>58→82</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>알멕</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-17</v>
+        <v>-23</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-525313600</v>
+        <v>-2847436800</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>0.20%→0.10%</t>
+          <t>1.06%→0.46%</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>32→15</t>
+          <t>40→17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>디앤디파마텍</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1414195200</v>
+        <v>1604064000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>2.74%→2.97%</t>
+          <t>0.95%→1.34%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>144→160</t>
+          <t>59→80</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>RFHIC</t>
+          <t>대주전자재료</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-17</v>
+        <v>-22</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-878614400</v>
+        <v>-1767744000</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.93%→0.63%</t>
+          <t>1.31%→0.88%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>75→58</t>
+          <t>72→50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>티에프이</t>
+          <t>가온칩스</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>475564800</v>
+        <v>968192000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.46%→0.58%</t>
+          <t>1.21%→1.66%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>58→70</t>
+          <t>137→157</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>에스앤에스텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-3006156800</v>
+        <v>-935456000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>3.06%→2.68%</t>
+          <t>0.76%→0.55%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>84→68</t>
+          <t>74→54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>459940800</v>
+        <v>1226905600</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.61%</t>
+          <t>2.74%→2.69%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>59→70</t>
+          <t>144→160</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-473184000</v>
+        <v>-1251507200</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>1.53%→1.42%</t>
+          <t>0.48%→0.17%</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>31→12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>467728000</v>
+        <v>442481600</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.86%→1.84%</t>
+          <t>0.51%→0.62%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>59→70</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>대주전자재료</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-11</v>
+        <v>-17</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-890419200</v>
+        <v>-470505600</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.31%→1.04%</t>
+          <t>0.20%→0.09%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>72→61</t>
+          <t>32→15</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>418624000</v>
+        <v>444416000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.25%→0.32%</t>
+          <t>1.86%→1.83%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RFHIC</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-498976000</v>
+        <v>-795137600</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.48%→1.37%</t>
+          <t>0.93%→0.59%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>141→131</t>
+          <t>75→58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>973747200</v>
+        <v>414160000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>4.04%→4.29%</t>
+          <t>0.25%→0.34%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>160→168</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-6</v>
+        <v>-16</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-979104000</v>
+        <v>-2929971200</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.36%→1.23%</t>
+          <t>3.06%→2.73%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>84→68</t>
         </is>
       </c>
     </row>
@@ -1283,98 +1283,130 @@
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>945772800</v>
+        <v>1389792000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>3.42%→3.77%</t>
+          <t>3.42%→4.14%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>126→133</t>
+          <t>126→136</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>비츠로셀</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-4</v>
+        <v>-15</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-477350400</v>
+        <v>-430776000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>2.21%→1.93%</t>
+          <t>0.69%→0.47%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>81→77</t>
+          <t>90→75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1584720000</v>
+        <v>857881600</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.61%→2.93%</t>
+          <t>4.04%→3.95%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="n"/>
-      <c r="H21" s="17" t="n"/>
-      <c r="I21" s="17" t="n"/>
-      <c r="J21" s="17" t="n"/>
-      <c r="K21" s="17" t="n"/>
+          <t>160→168</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>솔브레인홀딩스</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-423633600</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.60%→0.46%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>78→65</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>413168000</v>
+        <v>1639280000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.75%→2.96%</t>
+          <t>2.61%→3.16%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="n"/>
-      <c r="H22" s="17" t="n"/>
-      <c r="I22" s="17" t="n"/>
-      <c r="J22" s="17" t="n"/>
-      <c r="K22" s="17" t="n"/>
+          <t>39→44</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-454732800</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>1.53%→1.43%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>184→172</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1386,11 +1418,11 @@
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1607040000</v>
+        <v>1569840000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>3.67%→3.84%</t>
+          <t>3.67%→3.92%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -1398,1055 +1430,1397 @@
           <t>52→57</t>
         </is>
       </c>
-      <c r="G23" s="17" t="n"/>
-      <c r="H23" s="17" t="n"/>
-      <c r="I23" s="17" t="n"/>
-      <c r="J23" s="17" t="n"/>
-      <c r="K23" s="17" t="n"/>
-    </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,227억   ·   현금 38억(0.9%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-518816000</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>1.48%→1.49%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>141→131</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>코미코</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>394816000</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>2.75%→2.96%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>166→171</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-964224000</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>1.36%→1.27%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>42→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <v>-410092800</v>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>0.94%→0.76%</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>57→51</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="19" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 52억(1.9%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 4종목  /  매도 5종목</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <v>-449574400</v>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>2.21%→1.90%</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>81→77</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <v>-591628800</v>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>0.40%→0.23%</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>11→7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="19" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,227억   ·   현금 23억(0.5%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 3종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="8" t="n"/>
+      <c r="J30" s="8" t="n"/>
+      <c r="K30" s="8" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J30" s="9" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B31" s="11" t="n">
-        <v>201</v>
-      </c>
-      <c r="C31" s="11" t="n">
-        <v>5968644750</v>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>6.49%→8.34%</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>549→750</t>
-        </is>
-      </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
-        <v>-86</v>
-      </c>
-      <c r="I31" s="15" t="n">
-        <v>-7351968000</v>
-      </c>
-      <c r="J31" s="16" t="inlineStr">
-        <is>
-          <t>4.76%→2.24%</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>156→70</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>엘앤씨바이오  (신규)</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B32" s="11" t="n">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>6617442500</v>
+        <v>443206720</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.48%</t>
+          <t>1.52%→1.34%</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>0→139</t>
+          <t>983→1,066</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>오스코텍</t>
         </is>
       </c>
       <c r="H32" s="15" t="n">
-        <v>-81</v>
+        <v>-49</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-4288990500</v>
+        <v>-855736000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>3.28%→1.37%</t>
+          <t>3.06%→2.68%</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>150→69</t>
+          <t>701→652</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>파마리서치  (신규)</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>7923737500</v>
+        <v>1264334400</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>0.00%→2.97%</t>
+          <t>8.03%→7.82%</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>0→35</t>
+          <t>682→709</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H33" s="15" t="n">
-        <v>-66</v>
+        <v>-21</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-8427144000</v>
+        <v>-409634400</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>9.28%→8.13%</t>
+          <t>1.65%→1.59%</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>236→170</t>
+          <t>366→345</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>1124208000</v>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>8.03%→8.48%</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>186→192</t>
+        </is>
+      </c>
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>녹십자</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <v>-856032000</v>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>3.12%→3.08%</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>195→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 52억(1.9%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 4종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K38" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>201</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>5968644750</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>6.49%→8.34%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>549→750</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-86</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-7351968000</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>4.76%→2.24%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>156→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>엘앤씨바이오  (신규)</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>6617442500</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.48%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>0→139</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-4288990500</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>3.28%→1.37%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>150→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치  (신규)</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>7923737500</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.97%</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>0→35</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-66</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-8427144000</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>9.28%→8.13%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>236→170</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
           <t>리가켐바이오</t>
         </is>
       </c>
-      <c r="B34" s="11" t="n">
+      <c r="B42" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="C34" s="11" t="n">
+      <c r="C42" s="11" t="n">
         <v>1319378500</v>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>1.32%→1.71%</t>
         </is>
       </c>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>42→59</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
+      <c r="G42" s="14" t="inlineStr">
         <is>
           <t>하나마이크론</t>
         </is>
       </c>
-      <c r="H34" s="15" t="n">
+      <c r="H42" s="15" t="n">
         <v>-58</v>
       </c>
-      <c r="I34" s="15" t="n">
+      <c r="I42" s="15" t="n">
         <v>-1517686000</v>
       </c>
-      <c r="J34" s="16" t="inlineStr">
+      <c r="J42" s="16" t="inlineStr">
         <is>
           <t>2.38%→1.87%</t>
         </is>
       </c>
-      <c r="K34" s="13" t="inlineStr">
+      <c r="K42" s="13" t="inlineStr">
         <is>
           <t>249→191</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="17" t="n"/>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="G35" s="14" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="17" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="G43" s="14" t="inlineStr">
         <is>
           <t>기가비스</t>
         </is>
       </c>
-      <c r="H35" s="15" t="n">
+      <c r="H43" s="15" t="n">
         <v>-40</v>
       </c>
-      <c r="I35" s="15" t="n">
+      <c r="I43" s="15" t="n">
         <v>-4438800000</v>
       </c>
-      <c r="J35" s="16" t="inlineStr">
+      <c r="J43" s="16" t="inlineStr">
         <is>
           <t>3.71%→2.49%</t>
         </is>
       </c>
-      <c r="K35" s="13" t="inlineStr">
+      <c r="K43" s="13" t="inlineStr">
         <is>
           <t>100→60</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 53억(2.1%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="19" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 344억   ·   현금 5억(100.0%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 10종목  /  매도 14종목</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="G49" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C42" s="9" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G50" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H50" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I50" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J42" s="9" t="inlineStr">
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="K50" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B43" s="11" t="n">
-        <v>209</v>
-      </c>
-      <c r="C43" s="11" t="n">
-        <v>151713100</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>6.42%→6.86%</t>
-        </is>
-      </c>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>3,020→3,229</t>
-        </is>
-      </c>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>씨에스베어링</t>
-        </is>
-      </c>
-      <c r="H43" s="15" t="n">
-        <v>-318</v>
-      </c>
-      <c r="I43" s="15" t="n">
-        <v>-105146700</v>
-      </c>
-      <c r="J43" s="16" t="inlineStr">
-        <is>
-          <t>2.96%→2.65%</t>
-        </is>
-      </c>
-      <c r="K43" s="13" t="inlineStr">
-        <is>
-          <t>3,054→2,736</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>85</v>
-      </c>
-      <c r="C44" s="11" t="n">
-        <v>283581250</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>6.15%→6.97%</t>
-        </is>
-      </c>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>629→714</t>
-        </is>
-      </c>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>서부T&amp;D</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I44" s="15" t="n">
-        <v>-33323400</v>
-      </c>
-      <c r="J44" s="16" t="inlineStr">
-        <is>
-          <t>0.20%→0.10%</t>
-        </is>
-      </c>
-      <c r="K44" s="13" t="inlineStr">
-        <is>
-          <t>73→37</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>에프앤가이드</t>
-        </is>
-      </c>
-      <c r="B45" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C45" s="11" t="n">
-        <v>77792000</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>2.34%→2.56%</t>
-        </is>
-      </c>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>451→495</t>
-        </is>
-      </c>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H45" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I45" s="15" t="n">
-        <v>-100827000</v>
-      </c>
-      <c r="J45" s="16" t="inlineStr">
-        <is>
-          <t>6.01%→5.71%</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>733→697</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="B46" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C46" s="11" t="n">
-        <v>162129000</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>2.12%→2.59%</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>196→240</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>더핑크퐁컴퍼니</t>
-        </is>
-      </c>
-      <c r="H46" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I46" s="15" t="n">
-        <v>-29189000</v>
-      </c>
-      <c r="J46" s="16" t="inlineStr">
-        <is>
-          <t>0.21%→0.12%</t>
-        </is>
-      </c>
-      <c r="K46" s="13" t="inlineStr">
-        <is>
-          <t>82→48</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>네패스아크</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="C47" s="11" t="n">
-        <v>52360000</v>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>0.20%→0.35%</t>
-        </is>
-      </c>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>21→37</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>채비  (편출)</t>
-        </is>
-      </c>
-      <c r="H47" s="15" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I47" s="15" t="n">
-        <v>-15432600</v>
-      </c>
-      <c r="J47" s="16" t="inlineStr">
-        <is>
-          <t>0.05%→0.00%</t>
-        </is>
-      </c>
-      <c r="K47" s="13" t="inlineStr">
-        <is>
-          <t>34→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="10" t="inlineStr">
-        <is>
-          <t>알멕</t>
-        </is>
-      </c>
-      <c r="B48" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="C48" s="11" t="n">
-        <v>35572500</v>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>0.58%→0.68%</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>83→98</t>
-        </is>
-      </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>삼현  (편출)</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I48" s="15" t="n">
-        <v>-71833500</v>
-      </c>
-      <c r="J48" s="16" t="inlineStr">
-        <is>
-          <t>0.21%→0.00%</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>27→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
-        <is>
-          <t>HPSP</t>
-        </is>
-      </c>
-      <c r="B49" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>35615000</v>
-      </c>
-      <c r="D49" s="12" t="inlineStr">
-        <is>
-          <t>1.19%→1.29%</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>114→124</t>
-        </is>
-      </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>-25</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <v>-59818750</v>
-      </c>
-      <c r="J49" s="16" t="inlineStr">
-        <is>
-          <t>0.67%→0.49%</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>95→70</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="B50" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C50" s="11" t="n">
-        <v>84864000</v>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>2.64%→2.89%</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>85→93</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>오로스테크놀로지</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="n">
-        <v>-22</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <v>-34782000</v>
-      </c>
-      <c r="J50" s="16" t="inlineStr">
-        <is>
-          <t>0.39%→0.29%</t>
-        </is>
-      </c>
-      <c r="K50" s="13" t="inlineStr">
-        <is>
-          <t>85→63</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
-        <v>6</v>
+        <v>209</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>36006000</v>
+        <v>151713100</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>0.86%→0.97%</t>
+          <t>6.42%→6.86%</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>49→55</t>
+          <t>3,020→3,229</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
         <is>
-          <t>하이록코리아</t>
+          <t>씨에스베어링</t>
         </is>
       </c>
       <c r="H51" s="15" t="n">
-        <v>-14</v>
+        <v>-318</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-36592500</v>
+        <v>-105146700</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.10%</t>
+          <t>2.96%→2.65%</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>27→13</t>
+          <t>3,054→2,736</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>283581250</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>6.15%→6.97%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>629→714</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-100827000</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>6.01%→5.71%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>733→697</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>162129000</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>2.12%→2.59%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>196→240</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>서부T&amp;D</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-33323400</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.10%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>73→37</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>77792000</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>2.34%→2.56%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>451→495</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>더핑크퐁컴퍼니</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-29189000</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>0.21%→0.12%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>82→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>네패스아크</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>52360000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>0.20%→0.35%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>21→37</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>채비  (편출)</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-15432600</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.05%→0.00%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>34→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>35572500</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>0.58%→0.68%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>83→98</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>삼현  (편출)</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-71833500</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>0.21%→0.00%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>35615000</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>1.19%→1.29%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>114→124</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-59818750</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>0.67%→0.49%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>95→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>84864000</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>2.64%→2.89%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>85→93</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-34782000</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>0.39%→0.29%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>85→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>36006000</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>0.86%→0.97%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>49→55</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>하이록코리아</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-36592500</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>0.21%→0.10%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>27→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
           <t>코스메카코리아  (신규)</t>
         </is>
       </c>
-      <c r="B52" s="11" t="n">
+      <c r="B60" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C52" s="11" t="n">
+      <c r="C60" s="11" t="n">
         <v>37697500</v>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>0.00%→0.11%</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>0→5</t>
         </is>
       </c>
-      <c r="G52" s="14" t="inlineStr">
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H52" s="15" t="n">
+      <c r="H60" s="15" t="n">
         <v>-13</v>
       </c>
-      <c r="I52" s="15" t="n">
+      <c r="I60" s="15" t="n">
         <v>-154810500</v>
       </c>
-      <c r="J52" s="16" t="inlineStr">
+      <c r="J60" s="16" t="inlineStr">
         <is>
           <t>3.73%→3.28%</t>
         </is>
       </c>
-      <c r="K52" s="13" t="inlineStr">
+      <c r="K60" s="13" t="inlineStr">
         <is>
           <t>107→94</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="G53" s="14" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="17" t="n"/>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="G61" s="14" t="inlineStr">
         <is>
           <t>디앤디파마텍</t>
         </is>
       </c>
-      <c r="H53" s="15" t="n">
+      <c r="H61" s="15" t="n">
         <v>-10</v>
       </c>
-      <c r="I53" s="15" t="n">
+      <c r="I61" s="15" t="n">
         <v>-65450000</v>
       </c>
-      <c r="J53" s="16" t="inlineStr">
+      <c r="J61" s="16" t="inlineStr">
         <is>
           <t>0.92%→0.73%</t>
         </is>
       </c>
-      <c r="K53" s="13" t="inlineStr">
+      <c r="K61" s="13" t="inlineStr">
         <is>
           <t>48→38</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="n"/>
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="17" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="17" t="n"/>
-      <c r="G54" s="14" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="17" t="n"/>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
+      <c r="G62" s="14" t="inlineStr">
         <is>
           <t>ISC</t>
         </is>
       </c>
-      <c r="H54" s="15" t="n">
+      <c r="H62" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I54" s="15" t="n">
+      <c r="I62" s="15" t="n">
         <v>-91332500</v>
       </c>
-      <c r="J54" s="16" t="inlineStr">
+      <c r="J62" s="16" t="inlineStr">
         <is>
           <t>1.83%→1.57%</t>
         </is>
       </c>
-      <c r="K54" s="13" t="inlineStr">
+      <c r="K62" s="13" t="inlineStr">
         <is>
           <t>48→41</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="17" t="n"/>
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="17" t="n"/>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="17" t="n"/>
-      <c r="G55" s="14" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
         <is>
           <t>실리콘투</t>
         </is>
       </c>
-      <c r="H55" s="15" t="n">
+      <c r="H63" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I55" s="15" t="n">
+      <c r="I63" s="15" t="n">
         <v>-19558500</v>
       </c>
-      <c r="J55" s="16" t="inlineStr">
+      <c r="J63" s="16" t="inlineStr">
         <is>
           <t>0.81%→0.75%</t>
         </is>
       </c>
-      <c r="K55" s="13" t="inlineStr">
+      <c r="K63" s="13" t="inlineStr">
         <is>
           <t>85→79</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="17" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="G56" s="14" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="G64" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H56" s="15" t="n">
+      <c r="H64" s="15" t="n">
         <v>-3</v>
       </c>
-      <c r="I56" s="15" t="n">
+      <c r="I64" s="15" t="n">
         <v>-58522500</v>
       </c>
-      <c r="J56" s="16" t="inlineStr">
+      <c r="J64" s="16" t="inlineStr">
         <is>
           <t>2.69%→2.51%</t>
         </is>
       </c>
-      <c r="K56" s="13" t="inlineStr">
+      <c r="K64" s="13" t="inlineStr">
         <is>
           <t>47→44</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 18억(3.2%)      오늘 2026-07-14  vs  5일전 2026-07-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="4" t="n"/>
-      <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="B66" s="4" t="n"/>
+      <c r="C66" s="4" t="n"/>
+      <c r="D66" s="4" t="n"/>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="19" customHeight="1">
-      <c r="A61" s="19" t="inlineStr">
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B61" s="20" t="n"/>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="20" t="n"/>
-      <c r="G61" s="20" t="n"/>
-      <c r="H61" s="20" t="n"/>
-      <c r="I61" s="20" t="n"/>
-      <c r="J61" s="20" t="n"/>
-      <c r="K61" s="20" t="n"/>
+      <c r="B69" s="20" t="n"/>
+      <c r="C69" s="20" t="n"/>
+      <c r="D69" s="20" t="n"/>
+      <c r="E69" s="20" t="n"/>
+      <c r="F69" s="20" t="n"/>
+      <c r="G69" s="20" t="n"/>
+      <c r="H69" s="20" t="n"/>
+      <c r="I69" s="20" t="n"/>
+      <c r="J69" s="20" t="n"/>
+      <c r="K69" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A61:K61"/>
-    <mergeCell ref="A58:K58"/>
-    <mergeCell ref="A29:E29"/>
+  <mergeCells count="19">
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A66:K66"/>
+    <mergeCell ref="G49:K49"/>
+    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G29:K29"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A59:K59"/>
-    <mergeCell ref="A25:K25"/>
-    <mergeCell ref="A41:E41"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G41:K41"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A29:K29"/>
+    <mergeCell ref="A67:K67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260714.xlsx
+++ b/reports/pdf_rolling5_20260714.xlsx
@@ -1235,23 +1235,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>와이지엔터테인먼트</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>414160000</v>
+        <v>1389792000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.25%→0.34%</t>
+          <t>3.42%→4.14%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>27→37</t>
+          <t>126→136</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1279,23 +1279,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>와이지엔터테인먼트</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1389792000</v>
+        <v>414160000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>3.42%→4.14%</t>
+          <t>0.25%→0.34%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>126→136</t>
+          <t>27→37</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1367,23 +1367,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1639280000</v>
+        <v>1569840000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.61%→3.16%</t>
+          <t>3.67%→3.92%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1411,23 +1411,23 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B23" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>1569840000</v>
+        <v>1639280000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>3.67%→3.92%</t>
+          <t>2.61%→3.16%</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
